--- a/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 05/03. Xác nhận bảo hành/XNBH_AnhTuanNB_140526.xlsx
+++ b/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 05/03. Xác nhận bảo hành/XNBH_AnhTuanNB_140526.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 05\03. Xác nhận bảo hành\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6165B4A-C04C-4EFD-8958-92F24F7A5A63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D090D7E-3B36-4945-BE46-DC3986DFA517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -589,6 +589,75 @@
     <xf numFmtId="49" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="17" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -600,75 +669,6 @@
     </xf>
     <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1048,78 +1048,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="9" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="45"/>
-      <c r="B1" s="46"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="36" t="s">
+      <c r="A1" s="46"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
     </row>
     <row r="2" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="48"/>
-      <c r="B2" s="49"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="38" t="s">
+      <c r="A2" s="49"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
     </row>
     <row r="3" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="48"/>
-      <c r="B3" s="49"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="38" t="s">
+      <c r="A3" s="49"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
     </row>
     <row r="4" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="51"/>
-      <c r="B4" s="52"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="40" t="s">
+      <c r="A4" s="52"/>
+      <c r="B4" s="53"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="41" t="s">
         <v>48</v>
       </c>
-      <c r="E4" s="41"/>
-      <c r="F4" s="41"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="41"/>
-      <c r="I4" s="41"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="42"/>
+      <c r="H4" s="42"/>
+      <c r="I4" s="42"/>
     </row>
     <row r="5" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="42" t="s">
+      <c r="A5" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="43"/>
-      <c r="C5" s="43"/>
-      <c r="D5" s="44"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="44"/>
+      <c r="B5" s="44"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
     </row>
     <row r="6" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="32" t="s">
+      <c r="A6" s="55" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="32"/>
-      <c r="C6" s="32"/>
-      <c r="D6" s="32"/>
-      <c r="E6" s="32"/>
+      <c r="B6" s="55"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="55"/>
       <c r="F6" s="12"/>
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
@@ -1128,26 +1128,26 @@
       </c>
     </row>
     <row r="7" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="34" t="s">
+      <c r="A7" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="34"/>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
+      <c r="B7" s="57"/>
+      <c r="C7" s="57"/>
+      <c r="D7" s="57"/>
+      <c r="E7" s="57"/>
       <c r="F7" s="13"/>
       <c r="G7" s="13"/>
       <c r="H7" s="13"/>
       <c r="I7" s="13"/>
     </row>
     <row r="8" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="35" t="s">
+      <c r="A8" s="58" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="35"/>
-      <c r="C8" s="35"/>
-      <c r="D8" s="35"/>
-      <c r="E8" s="35"/>
+      <c r="B8" s="58"/>
+      <c r="C8" s="58"/>
+      <c r="D8" s="58"/>
+      <c r="E8" s="58"/>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
       <c r="H8" s="11"/>
@@ -1157,13 +1157,13 @@
       </c>
     </row>
     <row r="9" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="35" t="s">
+      <c r="A9" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="35"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="35"/>
+      <c r="B9" s="58"/>
+      <c r="C9" s="58"/>
+      <c r="D9" s="58"/>
+      <c r="E9" s="58"/>
       <c r="F9" s="11"/>
       <c r="G9" s="11"/>
       <c r="H9" s="11"/>
@@ -1391,7 +1391,7 @@
     </row>
     <row r="19" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="25">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B19" s="25" t="s">
         <v>22</v>
@@ -1414,7 +1414,7 @@
     </row>
     <row r="20" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="25">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B20" s="25" t="s">
         <v>22</v>
@@ -1437,7 +1437,7 @@
     </row>
     <row r="21" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="25">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B21" s="25" t="s">
         <v>22</v>
@@ -1460,7 +1460,7 @@
     </row>
     <row r="22" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="25">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B22" s="25" t="s">
         <v>22</v>
@@ -1483,7 +1483,7 @@
     </row>
     <row r="23" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="25">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B23" s="25" t="s">
         <v>22</v>
@@ -1520,47 +1520,47 @@
       </c>
       <c r="E25" s="10"/>
       <c r="F25" s="10"/>
-      <c r="G25" s="33"/>
-      <c r="H25" s="33"/>
-      <c r="I25" s="33"/>
+      <c r="G25" s="56"/>
+      <c r="H25" s="56"/>
+      <c r="I25" s="56"/>
     </row>
     <row r="26" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="56" t="s">
+      <c r="A26" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="B26" s="56"/>
-      <c r="C26" s="56"/>
-      <c r="D26" s="56" t="s">
+      <c r="B26" s="34"/>
+      <c r="C26" s="34"/>
+      <c r="D26" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="E26" s="56"/>
-      <c r="F26" s="56"/>
+      <c r="E26" s="34"/>
+      <c r="F26" s="34"/>
       <c r="G26" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="H26" s="55" t="s">
+      <c r="H26" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="I26" s="55"/>
+      <c r="I26" s="33"/>
     </row>
     <row r="27" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="58" t="s">
+      <c r="A27" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="B27" s="58"/>
-      <c r="C27" s="58"/>
-      <c r="D27" s="57" t="s">
+      <c r="B27" s="36"/>
+      <c r="C27" s="36"/>
+      <c r="D27" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="E27" s="57"/>
-      <c r="F27" s="57"/>
+      <c r="E27" s="35"/>
+      <c r="F27" s="35"/>
       <c r="G27" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="H27" s="57" t="s">
+      <c r="H27" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="I27" s="57"/>
+      <c r="I27" s="35"/>
     </row>
     <row r="28" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="16"/>
@@ -1618,23 +1618,23 @@
       <c r="I32" s="23"/>
     </row>
     <row r="33" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="56" t="s">
+      <c r="A33" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="B33" s="56"/>
-      <c r="C33" s="56"/>
-      <c r="D33" s="56" t="s">
+      <c r="B33" s="34"/>
+      <c r="C33" s="34"/>
+      <c r="D33" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="E33" s="56"/>
-      <c r="F33" s="56"/>
+      <c r="E33" s="34"/>
+      <c r="F33" s="34"/>
       <c r="G33" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="H33" s="56" t="s">
+      <c r="H33" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="I33" s="56"/>
+      <c r="I33" s="34"/>
       <c r="J33" s="8"/>
       <c r="K33" s="6"/>
       <c r="L33" s="6"/>
@@ -1651,12 +1651,23 @@
       <c r="I34" s="23"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B35" s="54"/>
-      <c r="C35" s="54"/>
+      <c r="B35" s="32"/>
+      <c r="C35" s="32"/>
     </row>
     <row r="74" ht="20.25" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="D1:I1"/>
+    <mergeCell ref="D2:I2"/>
+    <mergeCell ref="D3:I3"/>
+    <mergeCell ref="D4:I4"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A1:C4"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="H26:I26"/>
     <mergeCell ref="A26:C26"/>
@@ -1667,17 +1678,6 @@
     <mergeCell ref="A33:C33"/>
     <mergeCell ref="D33:F33"/>
     <mergeCell ref="H33:I33"/>
-    <mergeCell ref="D1:I1"/>
-    <mergeCell ref="D2:I2"/>
-    <mergeCell ref="D3:I3"/>
-    <mergeCell ref="D4:I4"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.51181102362204722" top="1.4960629921259843" bottom="0.98425196850393704" header="0.43307086614173229" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="78" orientation="landscape" r:id="rId1"/>

--- a/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 05/03. Xác nhận bảo hành/XNBH_AnhTuanNB_140526.xlsx
+++ b/4. Workspace/1. Bộ phận bảo hành/1. Thực hiện sửa chữa bảo hành/Năm 2026/Tháng 05/03. Xác nhận bảo hành/XNBH_AnhTuanNB_140526.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\4. Workspace\1. Bộ phận bảo hành\1. Thực hiện sửa chữa bảo hành\Năm 2026\Tháng 05\03. Xác nhận bảo hành\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D090D7E-3B36-4945-BE46-DC3986DFA517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01A79ED7-0420-405A-A94A-2D0581771B73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -66,9 +66,6 @@
     <t>ĐT: 0915 223 399</t>
   </si>
   <si>
-    <t>ĐC: AA46 TT19 KĐT Văn Quán, Phường Văn Quán, Quận Hà Đông, Hà Nội</t>
-  </si>
-  <si>
     <t xml:space="preserve">                                        </t>
   </si>
   <si>
@@ -181,6 +178,9 @@
   </si>
   <si>
     <t>Phụ Kiện</t>
+  </si>
+  <si>
+    <t>ĐC: A46 TT19 KĐT Văn Quán, Phường Văn Quán, Quận Hà Đông, Hà Nội</t>
   </si>
 </sst>
 </file>
@@ -504,7 +504,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -589,6 +589,66 @@
     <xf numFmtId="49" fontId="13" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -604,71 +664,8 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1048,106 +1045,106 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" s="9" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="46"/>
-      <c r="B1" s="47"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="37" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-      <c r="I1" s="38"/>
+      <c r="A1" s="43"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="57" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
     </row>
     <row r="2" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="49"/>
-      <c r="B2" s="50"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="39" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
+      <c r="A2" s="46"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="36" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
     </row>
     <row r="3" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="49"/>
-      <c r="B3" s="50"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="39" t="s">
+      <c r="A3" s="46"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
+      <c r="H3" s="37"/>
+      <c r="I3" s="37"/>
     </row>
     <row r="4" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="52"/>
-      <c r="B4" s="53"/>
-      <c r="C4" s="54"/>
-      <c r="D4" s="41" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4" s="42"/>
-      <c r="F4" s="42"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="42"/>
-      <c r="I4" s="42"/>
+      <c r="A4" s="49"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="39"/>
     </row>
     <row r="5" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="43" t="s">
+      <c r="A5" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="44"/>
-      <c r="C5" s="44"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="45"/>
-      <c r="I5" s="45"/>
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
     </row>
     <row r="6" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="55" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="55"/>
-      <c r="C6" s="55"/>
-      <c r="D6" s="55"/>
-      <c r="E6" s="55"/>
+      <c r="A6" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="32"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="32"/>
       <c r="F6" s="12"/>
       <c r="G6" s="12"/>
       <c r="H6" s="12"/>
       <c r="I6" s="31" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="57" t="s">
+      <c r="A7" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="57"/>
-      <c r="C7" s="57"/>
-      <c r="D7" s="57"/>
-      <c r="E7" s="57"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
       <c r="F7" s="13"/>
       <c r="G7" s="13"/>
       <c r="H7" s="13"/>
       <c r="I7" s="13"/>
     </row>
     <row r="8" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="58" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="58"/>
-      <c r="C8" s="58"/>
-      <c r="D8" s="58"/>
-      <c r="E8" s="58"/>
+      <c r="A8" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="35"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
       <c r="H8" s="11"/>
@@ -1157,13 +1154,13 @@
       </c>
     </row>
     <row r="9" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="58" t="s">
+      <c r="A9" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="58"/>
-      <c r="C9" s="58"/>
-      <c r="D9" s="58"/>
-      <c r="E9" s="58"/>
+      <c r="B9" s="35"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="35"/>
       <c r="F9" s="11"/>
       <c r="G9" s="11"/>
       <c r="H9" s="11"/>
@@ -1183,7 +1180,7 @@
         <v>2</v>
       </c>
       <c r="D10" s="28" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E10" s="28" t="s">
         <v>5</v>
@@ -1192,10 +1189,10 @@
         <v>7</v>
       </c>
       <c r="G10" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="H10" s="28" t="s">
         <v>49</v>
-      </c>
-      <c r="H10" s="28" t="s">
-        <v>50</v>
       </c>
       <c r="I10" s="28" t="s">
         <v>9</v>
@@ -1206,24 +1203,24 @@
         <v>1</v>
       </c>
       <c r="B11" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="29" t="s">
         <v>22</v>
-      </c>
-      <c r="C11" s="29" t="s">
-        <v>23</v>
       </c>
       <c r="D11" s="26"/>
       <c r="E11" s="26" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F11" s="26"/>
       <c r="G11" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="H11" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="H11" s="30" t="s">
-        <v>39</v>
-      </c>
       <c r="I11" s="26" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1231,24 +1228,24 @@
         <v>2</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D12" s="26"/>
       <c r="E12" s="26" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F12" s="26"/>
       <c r="G12" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="H12" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="H12" s="30" t="s">
-        <v>39</v>
-      </c>
       <c r="I12" s="26" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -1256,21 +1253,21 @@
         <v>3</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13" s="29" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D13" s="26"/>
       <c r="E13" s="26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F13" s="26"/>
       <c r="G13" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="H13" s="30" t="s">
         <v>40</v>
-      </c>
-      <c r="H13" s="30" t="s">
-        <v>41</v>
       </c>
       <c r="I13" s="26"/>
     </row>
@@ -1279,21 +1276,21 @@
         <v>4</v>
       </c>
       <c r="B14" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C14" s="29" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D14" s="26"/>
       <c r="E14" s="26" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F14" s="26"/>
       <c r="G14" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="H14" s="30" t="s">
         <v>40</v>
-      </c>
-      <c r="H14" s="30" t="s">
-        <v>41</v>
       </c>
       <c r="I14" s="26"/>
     </row>
@@ -1302,21 +1299,21 @@
         <v>5</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" s="29" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D15" s="26"/>
       <c r="E15" s="26" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F15" s="26"/>
       <c r="G15" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="H15" s="30" t="s">
         <v>40</v>
-      </c>
-      <c r="H15" s="30" t="s">
-        <v>41</v>
       </c>
       <c r="I15" s="26"/>
     </row>
@@ -1325,21 +1322,21 @@
         <v>6</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C16" s="29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D16" s="26"/>
       <c r="E16" s="26" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F16" s="26"/>
       <c r="G16" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="H16" s="30" t="s">
         <v>40</v>
-      </c>
-      <c r="H16" s="30" t="s">
-        <v>41</v>
       </c>
       <c r="I16" s="26"/>
     </row>
@@ -1348,21 +1345,21 @@
         <v>7</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C17" s="29" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D17" s="26"/>
       <c r="E17" s="26" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F17" s="26"/>
       <c r="G17" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="H17" s="30" t="s">
         <v>40</v>
-      </c>
-      <c r="H17" s="30" t="s">
-        <v>41</v>
       </c>
       <c r="I17" s="26"/>
     </row>
@@ -1371,21 +1368,21 @@
         <v>8</v>
       </c>
       <c r="B18" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C18" s="29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D18" s="26"/>
       <c r="E18" s="26" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F18" s="26"/>
       <c r="G18" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="H18" s="30" t="s">
         <v>40</v>
-      </c>
-      <c r="H18" s="30" t="s">
-        <v>41</v>
       </c>
       <c r="I18" s="26"/>
     </row>
@@ -1394,21 +1391,21 @@
         <v>9</v>
       </c>
       <c r="B19" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C19" s="29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" s="26"/>
       <c r="E19" s="26" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F19" s="26"/>
       <c r="G19" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="H19" s="30" t="s">
         <v>40</v>
-      </c>
-      <c r="H19" s="30" t="s">
-        <v>41</v>
       </c>
       <c r="I19" s="26"/>
     </row>
@@ -1417,21 +1414,21 @@
         <v>10</v>
       </c>
       <c r="B20" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C20" s="29" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D20" s="26"/>
       <c r="E20" s="26" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F20" s="26"/>
       <c r="G20" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="H20" s="30" t="s">
         <v>40</v>
-      </c>
-      <c r="H20" s="30" t="s">
-        <v>41</v>
       </c>
       <c r="I20" s="26"/>
     </row>
@@ -1440,21 +1437,21 @@
         <v>11</v>
       </c>
       <c r="B21" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C21" s="29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D21" s="26"/>
       <c r="E21" s="26" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F21" s="26"/>
       <c r="G21" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="H21" s="30" t="s">
         <v>40</v>
-      </c>
-      <c r="H21" s="30" t="s">
-        <v>41</v>
       </c>
       <c r="I21" s="26"/>
     </row>
@@ -1463,21 +1460,21 @@
         <v>12</v>
       </c>
       <c r="B22" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C22" s="29" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D22" s="26"/>
       <c r="E22" s="26" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F22" s="26"/>
       <c r="G22" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="H22" s="30" t="s">
         <v>40</v>
-      </c>
-      <c r="H22" s="30" t="s">
-        <v>41</v>
       </c>
       <c r="I22" s="26"/>
     </row>
@@ -1486,21 +1483,21 @@
         <v>13</v>
       </c>
       <c r="B23" s="25" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C23" s="29" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D23" s="26"/>
       <c r="E23" s="26" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F23" s="26"/>
       <c r="G23" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="H23" s="30" t="s">
         <v>40</v>
-      </c>
-      <c r="H23" s="30" t="s">
-        <v>41</v>
       </c>
       <c r="I23" s="26"/>
     </row>
@@ -1516,51 +1513,51 @@
     </row>
     <row r="25" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D25" s="10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E25" s="10"/>
       <c r="F25" s="10"/>
-      <c r="G25" s="56"/>
-      <c r="H25" s="56"/>
-      <c r="I25" s="56"/>
+      <c r="G25" s="33"/>
+      <c r="H25" s="33"/>
+      <c r="I25" s="33"/>
     </row>
     <row r="26" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="34" t="s">
-        <v>18</v>
-      </c>
-      <c r="B26" s="34"/>
-      <c r="C26" s="34"/>
-      <c r="D26" s="34" t="s">
+      <c r="A26" s="54" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26" s="54"/>
+      <c r="C26" s="54"/>
+      <c r="D26" s="54" t="s">
+        <v>43</v>
+      </c>
+      <c r="E26" s="54"/>
+      <c r="F26" s="54"/>
+      <c r="G26" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="H26" s="53" t="s">
         <v>44</v>
       </c>
-      <c r="E26" s="34"/>
-      <c r="F26" s="34"/>
-      <c r="G26" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="H26" s="33" t="s">
-        <v>45</v>
-      </c>
-      <c r="I26" s="33"/>
+      <c r="I26" s="53"/>
     </row>
     <row r="27" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="B27" s="36"/>
-      <c r="C27" s="36"/>
-      <c r="D27" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="E27" s="35"/>
-      <c r="F27" s="35"/>
+      <c r="A27" s="56" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" s="56"/>
+      <c r="C27" s="56"/>
+      <c r="D27" s="55" t="s">
+        <v>15</v>
+      </c>
+      <c r="E27" s="55"/>
+      <c r="F27" s="55"/>
       <c r="G27" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="H27" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="I27" s="35"/>
+        <v>15</v>
+      </c>
+      <c r="H27" s="55" t="s">
+        <v>15</v>
+      </c>
+      <c r="I27" s="55"/>
     </row>
     <row r="28" spans="1:9" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="16"/>
@@ -1618,23 +1615,23 @@
       <c r="I32" s="23"/>
     </row>
     <row r="33" spans="1:12" ht="15.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="34" t="s">
+      <c r="A33" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="B33" s="34"/>
-      <c r="C33" s="34"/>
-      <c r="D33" s="34" t="s">
+      <c r="B33" s="54"/>
+      <c r="C33" s="54"/>
+      <c r="D33" s="54" t="s">
+        <v>18</v>
+      </c>
+      <c r="E33" s="54"/>
+      <c r="F33" s="54"/>
+      <c r="G33" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E33" s="34"/>
-      <c r="F33" s="34"/>
-      <c r="G33" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="H33" s="34" t="s">
-        <v>42</v>
-      </c>
-      <c r="I33" s="34"/>
+      <c r="H33" s="54" t="s">
+        <v>41</v>
+      </c>
+      <c r="I33" s="54"/>
       <c r="J33" s="8"/>
       <c r="K33" s="6"/>
       <c r="L33" s="6"/>
@@ -1651,23 +1648,12 @@
       <c r="I34" s="23"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B35" s="32"/>
-      <c r="C35" s="32"/>
+      <c r="B35" s="52"/>
+      <c r="C35" s="52"/>
     </row>
     <row r="74" ht="20.25" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="A8:E8"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="D1:I1"/>
-    <mergeCell ref="D2:I2"/>
-    <mergeCell ref="D3:I3"/>
-    <mergeCell ref="D4:I4"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="A1:C4"/>
     <mergeCell ref="B35:C35"/>
     <mergeCell ref="H26:I26"/>
     <mergeCell ref="A26:C26"/>
@@ -1678,6 +1664,17 @@
     <mergeCell ref="A33:C33"/>
     <mergeCell ref="D33:F33"/>
     <mergeCell ref="H33:I33"/>
+    <mergeCell ref="D1:I1"/>
+    <mergeCell ref="D2:I2"/>
+    <mergeCell ref="D3:I3"/>
+    <mergeCell ref="D4:I4"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.51181102362204722" top="1.4960629921259843" bottom="0.98425196850393704" header="0.43307086614173229" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="78" orientation="landscape" r:id="rId1"/>
